--- a/media/shoblons/hospital/oth/otd_rep_1.xlsx
+++ b/media/shoblons/hospital/oth/otd_rep_1.xlsx
@@ -9,6 +9,9 @@
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Лист4" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t xml:space="preserve">ОТЧЕТ О РАБОТЕ</t>
   </si>
@@ -46,10 +49,10 @@
     <t xml:space="preserve">Травматологич.</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  КОЛИЧЕСТВО КОЕК (на конец года)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  КОЛИЧЕСТВО КОЕК (среднегодовых) </t>
+    <t xml:space="preserve">1. КОЛИЧЕСТВО КОЕК (на конец года)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. КОЛИЧЕСТВО КОЕК (среднегодовых) </t>
   </si>
   <si>
     <t xml:space="preserve">3. ПОСТУПИЛО БОЛЬНЫХ </t>
@@ -104,6 +107,141 @@
   </si>
   <si>
     <t xml:space="preserve">Выбыло из числа,поступивших в плановом поpядке </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удовлетворительных результатов не найдено </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Возраст выбывших</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всего выбыло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К/день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сред.к/д.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С лет.исход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Муж.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жен.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 — 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 — 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 — 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 — 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 — 59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 — 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 — 79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 и старше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВИДЫ ТРАВМ У БОЛЬНЫХ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N п/п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид травмы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выбыло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% к общ.числу травмиров.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в состоянии алк.опьянен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бытовая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уличная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прочая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дорожно-транспортная</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Итого</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РАСПРЕДЕЛЕНИЕ ВЫБЫВШИХ БОЛЬНЫХ ПО МЕСТУ ЖИТЕЛЬСТВА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Место жительство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кол-во выбывших</t>
+  </si>
+  <si>
+    <t xml:space="preserve">из них экстрен.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средн. К-день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прооперировано</t>
+  </si>
+  <si>
+    <t xml:space="preserve">из выбыв. Умерло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.г.Тюмень </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.Юг Тюмен.обл.(кроме Тюм.р-на)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.Тюменский р-н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.Ханты-Мансийский АО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.Ямало-Ненецкий АО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.Другие регионы России </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.Другие государства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Из сельской местности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всего иногородних</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;</t>
   </si>
 </sst>
 </file>
@@ -199,7 +337,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -232,8 +370,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -254,7 +404,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:D30"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.22"/>
@@ -487,11 +637,495 @@
     <mergeCell ref="A30:B30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.39375" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageMargins left="0.945138888888889" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:I12"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10.82"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:E8"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.71"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11"/>
+      <c r="B8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:F24"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.48"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/media/shoblons/hospital/oth/otd_rep_1.xlsx
+++ b/media/shoblons/hospital/oth/otd_rep_1.xlsx
@@ -12,7 +12,11 @@
     <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Лист4" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Лист5" sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Лист5!$6:$6</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -23,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="79">
   <si>
     <t xml:space="preserve">ОТЧЕТ О РАБОТЕ</t>
   </si>
@@ -43,12 +47,6 @@
     <t xml:space="preserve">Всего</t>
   </si>
   <si>
-    <t xml:space="preserve">Ортопедический</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Травматологич.</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. КОЛИЧЕСТВО КОЕК (на конец года)</t>
   </si>
   <si>
@@ -76,7 +74,7 @@
     <t xml:space="preserve">7. ПЛАН КОЙКО-ДНЕЙ</t>
   </si>
   <si>
-    <t xml:space="preserve">( 9 x Среднегод.к-во коек - К/дни на ремонт)</t>
+    <t xml:space="preserve">( 29 x Среднегод.к-во коек - К/дни на ремонт)</t>
   </si>
   <si>
     <t xml:space="preserve">8. ФАКТ КОЙКО-ДНЕЙ</t>
@@ -85,19 +83,29 @@
     <t xml:space="preserve">кроме то реанимационные</t>
   </si>
   <si>
-    <t xml:space="preserve">9. СРЕД.ДЛИТ-ТЬ ПРЕБЫВ-Я Б-ГО НА КОЙКЕ</t>
+    <t xml:space="preserve">9.СРЕДНЯЯ ЗАНЯТОСТЬ КОЙТИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">факт.к/дней — к/дни рефнимац.+ К/дни
+Закрытия на ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество коек среднегод.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. СРЕД.ДЛИТ-ТЬ ПРЕБЫВ-Я Б-ГО НА КОЙКЕ</t>
   </si>
   <si>
     <t xml:space="preserve">(Факт.к/дней-к/дни реанимац. : Кол-во пользовано б-х ) </t>
   </si>
   <si>
-    <t xml:space="preserve">10. ОБОРОТ КОЙКИ </t>
+    <t xml:space="preserve">11. ОБОРОТ КОЙКИ </t>
   </si>
   <si>
     <t xml:space="preserve">(Пользовано больных : к-во коек среднегод.) </t>
   </si>
   <si>
-    <t xml:space="preserve">11. ЛЕТАЛЬНОСТЬ </t>
+    <t xml:space="preserve">12. ЛЕТАЛЬНОСТЬ </t>
   </si>
   <si>
     <t xml:space="preserve">(К-во умер. : К-во выбывших * 100) </t>
@@ -241,7 +249,26 @@
     <t xml:space="preserve">Всего иногородних</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;</t>
+    <t xml:space="preserve">РАСПРЕДЕЛЕНИЕ ВЫБЫВШИХ БОЛЬНЫХ ПО НАПРАВИВШИМ УЧРЕЖДЕНИЯМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Направившее учреждение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кол-во
+Выбывших</t>
+  </si>
+  <si>
+    <t xml:space="preserve">из них
+Экстрен.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средн.
+К-день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">из выбыв
+Умерло</t>
   </si>
 </sst>
 </file>
@@ -282,7 +309,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -311,6 +338,27 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -337,7 +385,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -364,6 +412,30 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -403,10 +475,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:D30"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:D35"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="47.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.22"/>
   </cols>
   <sheetData>
@@ -461,169 +533,194 @@
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="8"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="8"/>
-    </row>
+      <c r="B32" s="14"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:D2"/>
@@ -633,8 +730,8 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.945138888888889" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
@@ -652,7 +749,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I12"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.62"/>
@@ -663,7 +760,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -676,149 +773,149 @@
     </row>
     <row r="3" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="A4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
+      <c r="A5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="A6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
+      <c r="A7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="A8" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
+      <c r="A9" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
+      <c r="A10" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="A11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -840,7 +937,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:E8"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.16"/>
@@ -849,7 +946,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -858,73 +955,73 @@
     </row>
     <row r="3" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="16" t="s">
         <v>48</v>
       </c>
+      <c r="C3" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="B7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+        <v>56</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -945,8 +1042,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F24"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:F16"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.48"/>
@@ -954,7 +1051,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -989,129 +1086,124 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>57</v>
+      <c r="A6" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+        <v>64</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+        <v>66</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+        <v>67</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+        <v>68</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+        <v>69</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+        <v>70</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+        <v>56</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
         <v>72</v>
       </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1128,4 +1220,90 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:F6"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.78"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>